--- a/SGC-CKN/Excel/699b36eb-b45c-4fce-9498-1dfddb16b411_Lô_CT-02_P7-91_D800_27-03-2026.xlsx
+++ b/SGC-CKN/Excel/699b36eb-b45c-4fce-9498-1dfddb16b411_Lô_CT-02_P7-91_D800_27-03-2026.xlsx
@@ -418,17 +418,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -454,6 +449,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -599,53 +599,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1266,7 +1266,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-9.44</v>
+        <v>-3.44</v>
       </c>
       <c r="G11" s="5">
         <v>-7.33</v>
@@ -1275,10 +1275,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>7.33</v>
+        <v>3.89</v>
       </c>
       <c r="J11" s="8">
-        <v>4.22</v>
+        <v>7.78</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1312,7 +1312,7 @@
       <c r="I12" s="9">
         <v>2.07</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>6.54</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1320,177 +1320,177 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-9.4</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-17.55</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>0.82</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>8.15</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="8">
         <v>9.98</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>-17.55</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-21.85</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.65</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>4.3</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>6.62</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-21.85</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-25.85</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.48</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>4</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>8.28</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-25.85</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-35.25</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.65</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>9.4</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>14.46</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-35.25</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-37.77</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>0.57</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>2.52</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="27">
         <v>4.45</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       <c r="I18" s="28">
         <v>1.73</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="27">
         <v>4.32</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1557,7 +1557,7 @@
       <c r="I19" s="31">
         <v>4.17</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="27">
         <v>2.91</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1592,7 +1592,7 @@
       <c r="I20" s="34">
         <v>1.15</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="27">
         <v>2.46</v>
       </c>
       <c r="K20" s="35" t="s">
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-9.44</v>
+        <v>-3.44</v>
       </c>
       <c r="F2" s="5">
         <v>-7.33</v>
@@ -1757,10 +1757,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>7.33</v>
-      </c>
-      <c r="I2" s="12">
-        <v>14.66</v>
+        <v>3.89</v>
+      </c>
+      <c r="I2" s="8">
+        <v>7.78</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1788,152 +1788,152 @@
       <c r="H3" s="9">
         <v>2.07</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>6.54</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-9.4</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-17.55</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>0.82</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>8.15</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>9.98</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-17.55</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-21.85</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.65</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>4.3</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>6.62</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-21.85</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-25.85</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>0.48</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>4</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>8.28</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-25.85</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>-35.25</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>0.65</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>9.4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>14.46</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-35.25</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-37.77</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>0.57</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>2.52</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="27">
         <v>4.45</v>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       <c r="H9" s="28">
         <v>1.73</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="27">
         <v>4.32</v>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       <c r="H10" s="31">
         <v>4.17</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="27">
         <v>2.91</v>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       <c r="H11" s="34">
         <v>1.15</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="27">
         <v>2.46</v>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-9.44</v>
+        <v>-3.44</v>
       </c>
       <c r="F12" s="39">
         <v>-44.82</v>
@@ -2047,10 +2047,10 @@
         <v>6.28</v>
       </c>
       <c r="H12" s="39">
-        <v>44.82</v>
+        <v>41.38</v>
       </c>
       <c r="I12" s="39">
-        <v>7.13</v>
+        <v>6.59</v>
       </c>
     </row>
   </sheetData>
